--- a/data/happinessbenelux.xlsx
+++ b/data/happinessbenelux.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luukn\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luukn\Documents\GitHub\happiness\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45F7C9F0-2F2B-4448-91D1-79492625098F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C3B1A5-0CC3-403C-97A1-1A7609917A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C79D878D-7F6F-4481-85A9-CBC35BA80EBA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Belgium</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>Country</t>
   </si>
 </sst>
 </file>
@@ -433,6 +436,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="B1">
         <v>2014</v>
       </c>
@@ -726,18 +732,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -759,14 +765,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{125E1A13-2F1B-4D71-A1D6-657CD05D596D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F548E6C0-0CBB-41E2-99A9-CFEBF169A790}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -780,4 +778,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{125E1A13-2F1B-4D71-A1D6-657CD05D596D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/happinessbenelux.xlsx
+++ b/data/happinessbenelux.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luukn\Documents\GitHub\happiness\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C3B1A5-0CC3-403C-97A1-1A7609917A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB722EA2-B360-4B07-A530-E252E2505ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C79D878D-7F6F-4481-85A9-CBC35BA80EBA}"/>
   </bookViews>
@@ -94,7 +94,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,40 +481,40 @@
         <v>0</v>
       </c>
       <c r="B2" s="2">
-        <v>6937</v>
+        <v>6.9370000000000003</v>
       </c>
       <c r="C2" s="2">
-        <v>6929</v>
+        <v>6.9290000000000003</v>
       </c>
       <c r="D2" s="2">
-        <v>6891</v>
+        <v>6.891</v>
       </c>
       <c r="E2" s="2">
-        <v>6927</v>
+        <v>6.9269999999999996</v>
       </c>
       <c r="F2" s="2">
-        <v>6923</v>
+        <v>6.923</v>
       </c>
       <c r="G2" s="2">
-        <v>6864</v>
+        <v>6.8639999999999999</v>
       </c>
       <c r="H2" s="2">
-        <v>6834</v>
+        <v>6.8339999999999996</v>
       </c>
       <c r="I2" s="2">
-        <v>6805</v>
+        <v>6.8049999999999997</v>
       </c>
       <c r="J2" s="2">
-        <v>6859</v>
+        <v>6.859</v>
       </c>
       <c r="K2" s="2">
-        <v>6894</v>
+        <v>6.8940000000000001</v>
       </c>
       <c r="L2" s="2">
-        <v>6910</v>
+        <v>6.91</v>
       </c>
       <c r="M2" s="2">
-        <v>6926</v>
+        <v>6.9260000000000002</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -522,40 +522,40 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>7378</v>
+        <v>7.3780000000000001</v>
       </c>
       <c r="C3" s="2">
-        <v>7339</v>
+        <v>7.3390000000000004</v>
       </c>
       <c r="D3" s="2">
-        <v>7377</v>
+        <v>7.3769999999999998</v>
       </c>
       <c r="E3" s="2">
-        <v>7441</v>
+        <v>7.4409999999999998</v>
       </c>
       <c r="F3" s="2">
-        <v>7488</v>
+        <v>7.4880000000000004</v>
       </c>
       <c r="G3" s="2">
-        <v>7449</v>
+        <v>7.4489999999999998</v>
       </c>
       <c r="H3" s="2">
-        <v>7464</v>
+        <v>7.4640000000000004</v>
       </c>
       <c r="I3" s="2">
-        <v>7415</v>
+        <v>7.415</v>
       </c>
       <c r="J3" s="2">
-        <v>7403</v>
+        <v>7.4029999999999996</v>
       </c>
       <c r="K3" s="2">
-        <v>7319</v>
+        <v>7.319</v>
       </c>
       <c r="L3" s="2">
-        <v>7306</v>
+        <v>7.306</v>
       </c>
       <c r="M3" s="2">
-        <v>7223</v>
+        <v>7.2229999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -563,40 +563,40 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>6946</v>
+        <v>6.9459999999999997</v>
       </c>
       <c r="C4" s="2">
-        <v>6871</v>
+        <v>6.8710000000000004</v>
       </c>
       <c r="D4" s="2">
-        <v>6863</v>
+        <v>6.8630000000000004</v>
       </c>
       <c r="E4" s="2">
-        <v>6910</v>
+        <v>6.91</v>
       </c>
       <c r="F4" s="2">
-        <v>7090</v>
+        <v>7.09</v>
       </c>
       <c r="G4" s="2">
-        <v>7238</v>
+        <v>7.2380000000000004</v>
       </c>
       <c r="H4" s="2">
-        <v>7324</v>
+        <v>7.3239999999999998</v>
       </c>
       <c r="I4" s="2">
-        <v>7404</v>
+        <v>7.4039999999999999</v>
       </c>
       <c r="J4" s="2">
-        <v>7228</v>
+        <v>7.2279999999999998</v>
       </c>
       <c r="K4" s="2">
-        <v>7122</v>
+        <v>7.1219999999999999</v>
       </c>
       <c r="L4" s="2">
-        <v>7122</v>
+        <v>7.1219999999999999</v>
       </c>
       <c r="M4" s="2">
-        <v>7063</v>
+        <v>7.0629999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -732,18 +732,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -765,6 +765,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{125E1A13-2F1B-4D71-A1D6-657CD05D596D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F548E6C0-0CBB-41E2-99A9-CFEBF169A790}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -778,12 +786,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{125E1A13-2F1B-4D71-A1D6-657CD05D596D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>